--- a/product_selector_out/STM32L4P5-Q5.xlsx
+++ b/product_selector_out/STM32L4P5-Q5.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4q5ag.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4q5ag.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4q5ag.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4q5ag.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4q5ag.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7493,9 +7493,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -7508,17 +7508,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7533,7 +7533,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7543,29 +7543,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
@@ -7578,27 +7578,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z12" s="8" t="inlineStr">
+      <c r="V12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7613,7 +7613,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC12" s="8" t="inlineStr">
+      <c r="AC12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7623,17 +7623,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG12" s="8" t="inlineStr">
+      <c r="AE12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7643,32 +7643,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN12" s="8" t="inlineStr">
+      <c r="AI12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7678,7 +7678,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AP12" s="8" t="inlineStr">
+      <c r="AP12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7698,29 +7698,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY12" s="6" t="inlineStr">
@@ -7743,42 +7743,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ12" s="8" t="inlineStr">
+      <c r="BC12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7793,9 +7793,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7820,9 +7820,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -7835,17 +7835,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7860,7 +7860,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="8" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7870,29 +7870,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
@@ -7905,27 +7905,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="8" t="inlineStr">
+      <c r="V13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7950,12 +7950,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF13" s="8" t="inlineStr">
+      <c r="AE13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7970,7 +7970,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="8" t="inlineStr">
+      <c r="AI13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7980,7 +7980,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK13" s="8" t="inlineStr">
+      <c r="AK13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7990,7 +7990,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AM13" s="8" t="inlineStr">
+      <c r="AM13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8025,12 +8025,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU13" s="8" t="inlineStr">
+      <c r="AT13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8040,14 +8040,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY13" s="6" t="inlineStr">
@@ -8070,42 +8070,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ13" s="8" t="inlineStr">
+      <c r="BC13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8120,9 +8120,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8147,9 +8147,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -8162,17 +8162,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8187,7 +8187,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8197,29 +8197,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -8232,27 +8232,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="8" t="inlineStr">
+      <c r="V14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8267,7 +8267,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC14" s="8" t="inlineStr">
+      <c r="AC14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8277,17 +8277,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG14" s="8" t="inlineStr">
+      <c r="AE14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8297,32 +8297,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN14" s="8" t="inlineStr">
+      <c r="AI14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8332,7 +8332,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AP14" s="8" t="inlineStr">
+      <c r="AP14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8352,12 +8352,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU14" s="8" t="inlineStr">
+      <c r="AT14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8367,14 +8367,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY14" s="6" t="inlineStr">
@@ -8397,42 +8397,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ14" s="8" t="inlineStr">
+      <c r="BC14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8447,9 +8447,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8474,9 +8474,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -8489,17 +8489,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8514,7 +8514,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8524,29 +8524,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -8559,27 +8559,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="8" t="inlineStr">
+      <c r="V15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8604,17 +8604,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG15" s="8" t="inlineStr">
+      <c r="AE15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8624,32 +8624,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN15" s="8" t="inlineStr">
+      <c r="AI15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8679,29 +8679,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY15" s="6" t="inlineStr">
@@ -8724,42 +8724,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ15" s="8" t="inlineStr">
+      <c r="BC15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8774,9 +8774,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8801,9 +8801,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -8816,17 +8816,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8841,7 +8841,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="8" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8851,29 +8851,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -8886,27 +8886,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z16" s="8" t="inlineStr">
+      <c r="V16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8921,7 +8921,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC16" s="8" t="inlineStr">
+      <c r="AC16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8931,12 +8931,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF16" s="8" t="inlineStr">
+      <c r="AE16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8951,7 +8951,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI16" s="8" t="inlineStr">
+      <c r="AI16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8961,7 +8961,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK16" s="8" t="inlineStr">
+      <c r="AK16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8971,7 +8971,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AM16" s="8" t="inlineStr">
+      <c r="AM16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9006,12 +9006,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU16" s="8" t="inlineStr">
+      <c r="AT16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9021,14 +9021,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY16" s="6" t="inlineStr">
@@ -9051,42 +9051,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ16" s="8" t="inlineStr">
+      <c r="BC16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9101,9 +9101,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9128,9 +9128,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -9143,17 +9143,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9168,7 +9168,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M17" s="8" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9178,29 +9178,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -9218,22 +9218,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z17" s="8" t="inlineStr">
+      <c r="W17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9248,7 +9248,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC17" s="8" t="inlineStr">
+      <c r="AC17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9258,12 +9258,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF17" s="8" t="inlineStr">
+      <c r="AE17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9278,7 +9278,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI17" s="8" t="inlineStr">
+      <c r="AI17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9288,7 +9288,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK17" s="8" t="inlineStr">
+      <c r="AK17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9298,7 +9298,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AM17" s="8" t="inlineStr">
+      <c r="AM17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9313,7 +9313,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AP17" s="8" t="inlineStr">
+      <c r="AP17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9333,12 +9333,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU17" s="8" t="inlineStr">
+      <c r="AT17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9348,14 +9348,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY17" s="6" t="inlineStr">
@@ -9378,42 +9378,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ17" s="8" t="inlineStr">
+      <c r="BC17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9428,9 +9428,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9455,9 +9455,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -9470,17 +9470,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9495,7 +9495,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M18" s="8" t="inlineStr">
+      <c r="M18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9505,29 +9505,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T18" s="6" t="inlineStr">
@@ -9545,22 +9545,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z18" s="8" t="inlineStr">
+      <c r="W18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9575,7 +9575,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC18" s="8" t="inlineStr">
+      <c r="AC18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9585,12 +9585,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF18" s="8" t="inlineStr">
+      <c r="AE18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9605,7 +9605,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI18" s="8" t="inlineStr">
+      <c r="AI18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9615,7 +9615,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK18" s="8" t="inlineStr">
+      <c r="AK18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9625,7 +9625,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AM18" s="8" t="inlineStr">
+      <c r="AM18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9660,12 +9660,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU18" s="8" t="inlineStr">
+      <c r="AT18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9675,14 +9675,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY18" s="6" t="inlineStr">
@@ -9705,42 +9705,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ18" s="8" t="inlineStr">
+      <c r="BC18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9755,9 +9755,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9782,9 +9782,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -9797,17 +9797,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9822,7 +9822,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M19" s="8" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9832,29 +9832,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T19" s="6" t="inlineStr">
@@ -9867,27 +9867,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z19" s="8" t="inlineStr">
+      <c r="V19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9907,22 +9907,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG19" s="8" t="inlineStr">
+      <c r="AD19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9932,32 +9932,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN19" s="8" t="inlineStr">
+      <c r="AI19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9987,29 +9987,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY19" s="6" t="inlineStr">
@@ -10032,42 +10032,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ19" s="8" t="inlineStr">
+      <c r="BC19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10082,9 +10082,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10109,9 +10109,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -10124,17 +10124,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10149,7 +10149,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M20" s="8" t="inlineStr">
+      <c r="M20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10159,29 +10159,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T20" s="6" t="inlineStr">
@@ -10194,27 +10194,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z20" s="8" t="inlineStr">
+      <c r="V20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10239,17 +10239,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG20" s="8" t="inlineStr">
+      <c r="AE20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10259,32 +10259,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN20" s="8" t="inlineStr">
+      <c r="AI20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10314,12 +10314,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU20" s="8" t="inlineStr">
+      <c r="AT20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10329,14 +10329,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY20" s="6" t="inlineStr">
@@ -10359,42 +10359,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ20" s="8" t="inlineStr">
+      <c r="BC20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10409,9 +10409,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10436,9 +10436,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -10451,17 +10451,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10476,7 +10476,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M21" s="8" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10486,29 +10486,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R21" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S21" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T21" s="6" t="inlineStr">
@@ -10521,27 +10521,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z21" s="8" t="inlineStr">
+      <c r="V21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10556,7 +10556,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC21" s="8" t="inlineStr">
+      <c r="AC21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10566,12 +10566,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF21" s="8" t="inlineStr">
+      <c r="AE21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10586,7 +10586,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI21" s="8" t="inlineStr">
+      <c r="AI21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10596,7 +10596,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK21" s="8" t="inlineStr">
+      <c r="AK21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10606,7 +10606,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AM21" s="8" t="inlineStr">
+      <c r="AM21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10641,29 +10641,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW21" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY21" s="6" t="inlineStr">
@@ -10686,42 +10686,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ21" s="8" t="inlineStr">
+      <c r="BC21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10736,9 +10736,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10763,9 +10763,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -10778,17 +10778,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10803,7 +10803,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M22" s="8" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10813,29 +10813,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
@@ -10848,27 +10848,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z22" s="8" t="inlineStr">
+      <c r="V22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10893,17 +10893,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG22" s="8" t="inlineStr">
+      <c r="AE22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10913,32 +10913,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN22" s="8" t="inlineStr">
+      <c r="AI22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10968,12 +10968,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU22" s="8" t="inlineStr">
+      <c r="AT22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10983,14 +10983,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY22" s="6" t="inlineStr">
@@ -11013,42 +11013,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ22" s="8" t="inlineStr">
+      <c r="BC22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11063,9 +11063,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11090,9 +11090,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -11105,17 +11105,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J23" s="8" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11130,7 +11130,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M23" s="8" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11140,29 +11140,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R23" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S23" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T23" s="6" t="inlineStr">
@@ -11175,27 +11175,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z23" s="8" t="inlineStr">
+      <c r="V23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11215,22 +11215,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG23" s="8" t="inlineStr">
+      <c r="AD23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11240,32 +11240,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN23" s="8" t="inlineStr">
+      <c r="AI23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11295,12 +11295,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU23" s="8" t="inlineStr">
+      <c r="AT23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11310,14 +11310,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW23" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY23" s="6" t="inlineStr">
@@ -11340,42 +11340,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ23" s="8" t="inlineStr">
+      <c r="BC23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11390,9 +11390,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11417,9 +11417,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -11432,17 +11432,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J24" s="8" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11457,7 +11457,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M24" s="8" t="inlineStr">
+      <c r="M24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11467,29 +11467,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R24" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S24" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T24" s="6" t="inlineStr">
@@ -11502,27 +11502,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z24" s="8" t="inlineStr">
+      <c r="V24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11547,17 +11547,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG24" s="8" t="inlineStr">
+      <c r="AE24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11567,32 +11567,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN24" s="8" t="inlineStr">
+      <c r="AI24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11622,12 +11622,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU24" s="8" t="inlineStr">
+      <c r="AT24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11637,14 +11637,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW24" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY24" s="6" t="inlineStr">
@@ -11667,42 +11667,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ24" s="8" t="inlineStr">
+      <c r="BC24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11717,9 +11717,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11744,7 +11744,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -11759,17 +11759,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J25" s="8" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11784,7 +11784,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M25" s="8" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11794,17 +11794,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q25" s="8" t="inlineStr">
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11829,27 +11829,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z25" s="8" t="inlineStr">
+      <c r="V25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11874,17 +11874,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG25" s="8" t="inlineStr">
+      <c r="AE25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11894,32 +11894,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN25" s="8" t="inlineStr">
+      <c r="AI25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11949,12 +11949,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU25" s="8" t="inlineStr">
+      <c r="AT25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11969,7 +11969,7 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX25" s="7" t="inlineStr">
+      <c r="AX25" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -11994,42 +11994,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ25" s="8" t="inlineStr">
+      <c r="BC25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12071,9 +12071,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -12086,17 +12086,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J26" s="8" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12111,7 +12111,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M26" s="8" t="inlineStr">
+      <c r="M26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12121,29 +12121,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R26" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S26" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T26" s="6" t="inlineStr">
@@ -12156,27 +12156,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z26" s="8" t="inlineStr">
+      <c r="V26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12191,7 +12191,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC26" s="8" t="inlineStr">
+      <c r="AC26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12201,17 +12201,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG26" s="8" t="inlineStr">
+      <c r="AE26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12221,32 +12221,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN26" s="8" t="inlineStr">
+      <c r="AI26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12256,7 +12256,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AP26" s="8" t="inlineStr">
+      <c r="AP26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12276,12 +12276,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU26" s="8" t="inlineStr">
+      <c r="AT26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12291,14 +12291,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW26" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY26" s="6" t="inlineStr">
@@ -12321,42 +12321,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ26" s="8" t="inlineStr">
+      <c r="BC26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12371,9 +12371,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -12398,9 +12398,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -12413,17 +12413,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J27" s="8" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12438,7 +12438,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M27" s="8" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12448,29 +12448,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T27" s="6" t="inlineStr">
@@ -12483,27 +12483,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z27" s="8" t="inlineStr">
+      <c r="V27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12518,7 +12518,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC27" s="8" t="inlineStr">
+      <c r="AC27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12528,12 +12528,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF27" s="8" t="inlineStr">
+      <c r="AE27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12548,7 +12548,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI27" s="8" t="inlineStr">
+      <c r="AI27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12558,7 +12558,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK27" s="8" t="inlineStr">
+      <c r="AK27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12568,7 +12568,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AM27" s="8" t="inlineStr">
+      <c r="AM27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12583,7 +12583,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AP27" s="8" t="inlineStr">
+      <c r="AP27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12603,29 +12603,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY27" s="6" t="inlineStr">
@@ -12648,42 +12648,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ27" s="8" t="inlineStr">
+      <c r="BC27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12698,9 +12698,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -12725,9 +12725,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -12740,17 +12740,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J28" s="8" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12765,7 +12765,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M28" s="8" t="inlineStr">
+      <c r="M28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12775,29 +12775,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T28" s="6" t="inlineStr">
@@ -12810,27 +12810,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z28" s="8" t="inlineStr">
+      <c r="V28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12845,7 +12845,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC28" s="8" t="inlineStr">
+      <c r="AC28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12855,17 +12855,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG28" s="8" t="inlineStr">
+      <c r="AE28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12875,32 +12875,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN28" s="8" t="inlineStr">
+      <c r="AI28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12910,7 +12910,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AP28" s="8" t="inlineStr">
+      <c r="AP28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12930,12 +12930,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU28" s="8" t="inlineStr">
+      <c r="AT28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12945,14 +12945,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY28" s="6" t="inlineStr">
@@ -12975,42 +12975,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ28" s="8" t="inlineStr">
+      <c r="BC28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13025,9 +13025,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -13067,17 +13067,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J29" s="8" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13092,7 +13092,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M29" s="8" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13102,17 +13102,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q29" s="8" t="inlineStr">
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13137,27 +13137,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z29" s="8" t="inlineStr">
+      <c r="V29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13182,17 +13182,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG29" s="8" t="inlineStr">
+      <c r="AE29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13202,32 +13202,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN29" s="8" t="inlineStr">
+      <c r="AI29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13257,17 +13257,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV29" s="8" t="inlineStr">
+      <c r="AT29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13277,7 +13277,7 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX29" s="7" t="inlineStr">
+      <c r="AX29" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -13302,42 +13302,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ29" s="8" t="inlineStr">
+      <c r="BC29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13373,7 +13373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13407,7 +13407,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STM32L4P5RE</t>
+          <t>STM32L4Q5AG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -13429,7 +13429,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32L4P5RE</t>
+          <t>STM32L4Q5AG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -13451,7 +13451,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32L4P5RE</t>
+          <t>STM32L4Q5AG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -13466,14 +13466,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32L4P5ZG</t>
+          <t>STM32L4P5AE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -13495,7 +13495,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32L4P5ZG</t>
+          <t>STM32L4P5AE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -13517,7 +13517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32L4P5ZG</t>
+          <t>STM32L4P5AE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -13532,1063 +13532,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>STM32L4Q5CG</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>STM32L4Q5CG</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STM32L4Q5CG</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>STM32L4P5ZE</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>STM32L4P5ZE</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>STM32L4P5ZE</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>STM32L4P5QG</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>STM32L4P5QG</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>STM32L4P5QG</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>STM32L4Q5RG</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>STM32L4Q5RG</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>STM32L4Q5RG</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>STM32L4P5VG</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>STM32L4P5VG</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>STM32L4P5VG</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>STM32L4P5QE</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>STM32L4P5QE</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>STM32L4P5QE</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>STM32L4Q5ZG</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>STM32L4Q5ZG</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>STM32L4Q5ZG</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>STM32L4P5VE</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>STM32L4P5VE</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>STM32L4P5VE</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>STM32L4Q5VG</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>STM32L4Q5VG</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>STM32L4Q5VG</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>STM32L4Q5QG</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>STM32L4Q5QG</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>STM32L4Q5QG</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>STM32L4P5AG</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>STM32L4P5AG</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>STM32L4P5AG</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>STM32L4Q5AG</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>STM32L4Q5AG</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>STM32L4Q5AG</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>STM32L4P5CG</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>STM32L4P5CG</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>STM32L4P5CG</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>STM32L4P5CE</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>STM32L4P5CE</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>STM32L4P5CE</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>STM32L4P5RG</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>STM32L4P5RG</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>STM32L4P5RG</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>STM32L4P5AE</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>STM32L4P5AE</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>STM32L4P5AE</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32L4P5-Q5.xlsx
+++ b/product_selector_out/STM32L4P5-Q5.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4q5ag.pdf</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4q5ag.pdf</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4q5ag.pdf</t>
         </is>
       </c>
     </row>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4q5ag.pdf</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4q5ag.pdf</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
     </row>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
     </row>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
     </row>
@@ -7493,9 +7493,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -7508,17 +7508,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7533,7 +7533,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="7" t="inlineStr">
+      <c r="M12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7543,29 +7543,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
@@ -7578,27 +7578,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z12" s="7" t="inlineStr">
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7613,7 +7613,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC12" s="7" t="inlineStr">
+      <c r="AC12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7623,17 +7623,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG12" s="7" t="inlineStr">
+      <c r="AE12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7643,32 +7643,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN12" s="7" t="inlineStr">
+      <c r="AI12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7678,7 +7678,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AP12" s="7" t="inlineStr">
+      <c r="AP12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7698,29 +7698,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY12" s="6" t="inlineStr">
@@ -7743,42 +7743,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ12" s="7" t="inlineStr">
+      <c r="BC12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7793,9 +7793,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -7820,9 +7820,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -7835,17 +7835,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7860,7 +7860,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="M13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7870,29 +7870,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
@@ -7905,27 +7905,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="7" t="inlineStr">
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7950,12 +7950,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF13" s="7" t="inlineStr">
+      <c r="AE13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7970,7 +7970,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="7" t="inlineStr">
+      <c r="AI13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7980,7 +7980,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK13" s="7" t="inlineStr">
+      <c r="AK13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7990,7 +7990,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AM13" s="7" t="inlineStr">
+      <c r="AM13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8025,12 +8025,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU13" s="7" t="inlineStr">
+      <c r="AT13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8040,14 +8040,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY13" s="6" t="inlineStr">
@@ -8070,42 +8070,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ13" s="7" t="inlineStr">
+      <c r="BC13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8120,9 +8120,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8147,9 +8147,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -8162,17 +8162,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8187,7 +8187,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="7" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8197,29 +8197,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -8232,27 +8232,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="7" t="inlineStr">
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8267,7 +8267,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC14" s="7" t="inlineStr">
+      <c r="AC14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8277,17 +8277,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG14" s="7" t="inlineStr">
+      <c r="AE14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8297,32 +8297,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN14" s="7" t="inlineStr">
+      <c r="AI14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8332,7 +8332,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AP14" s="7" t="inlineStr">
+      <c r="AP14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8352,12 +8352,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU14" s="7" t="inlineStr">
+      <c r="AT14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8367,14 +8367,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY14" s="6" t="inlineStr">
@@ -8397,42 +8397,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ14" s="7" t="inlineStr">
+      <c r="BC14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8447,9 +8447,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8474,9 +8474,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -8489,17 +8489,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8514,7 +8514,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr">
+      <c r="M15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8524,29 +8524,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -8559,27 +8559,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="7" t="inlineStr">
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8604,17 +8604,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG15" s="7" t="inlineStr">
+      <c r="AE15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8624,32 +8624,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN15" s="7" t="inlineStr">
+      <c r="AI15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8679,29 +8679,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY15" s="6" t="inlineStr">
@@ -8724,42 +8724,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ15" s="7" t="inlineStr">
+      <c r="BC15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8774,9 +8774,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8801,9 +8801,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -8816,17 +8816,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8841,7 +8841,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="7" t="inlineStr">
+      <c r="M16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8851,29 +8851,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -8886,27 +8886,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z16" s="7" t="inlineStr">
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8921,7 +8921,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC16" s="7" t="inlineStr">
+      <c r="AC16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8931,12 +8931,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF16" s="7" t="inlineStr">
+      <c r="AE16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8951,7 +8951,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI16" s="7" t="inlineStr">
+      <c r="AI16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8961,7 +8961,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK16" s="7" t="inlineStr">
+      <c r="AK16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8971,7 +8971,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AM16" s="7" t="inlineStr">
+      <c r="AM16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9006,12 +9006,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU16" s="7" t="inlineStr">
+      <c r="AT16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9021,14 +9021,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY16" s="6" t="inlineStr">
@@ -9051,42 +9051,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ16" s="7" t="inlineStr">
+      <c r="BC16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9101,9 +9101,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -9128,9 +9128,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -9143,17 +9143,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9168,7 +9168,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr">
+      <c r="M17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9178,29 +9178,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -9218,22 +9218,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z17" s="7" t="inlineStr">
+      <c r="W17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9248,7 +9248,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC17" s="7" t="inlineStr">
+      <c r="AC17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9258,12 +9258,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF17" s="7" t="inlineStr">
+      <c r="AE17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9278,7 +9278,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI17" s="7" t="inlineStr">
+      <c r="AI17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9288,7 +9288,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK17" s="7" t="inlineStr">
+      <c r="AK17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9298,7 +9298,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AM17" s="7" t="inlineStr">
+      <c r="AM17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9313,7 +9313,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AP17" s="7" t="inlineStr">
+      <c r="AP17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9333,12 +9333,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU17" s="7" t="inlineStr">
+      <c r="AT17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9348,14 +9348,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY17" s="6" t="inlineStr">
@@ -9378,42 +9378,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ17" s="7" t="inlineStr">
+      <c r="BC17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9428,9 +9428,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -9455,9 +9455,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -9470,17 +9470,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9495,7 +9495,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M18" s="7" t="inlineStr">
+      <c r="M18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9505,29 +9505,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T18" s="6" t="inlineStr">
@@ -9545,22 +9545,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z18" s="7" t="inlineStr">
+      <c r="W18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9575,7 +9575,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC18" s="7" t="inlineStr">
+      <c r="AC18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9585,12 +9585,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF18" s="7" t="inlineStr">
+      <c r="AE18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9605,7 +9605,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI18" s="7" t="inlineStr">
+      <c r="AI18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9615,7 +9615,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK18" s="7" t="inlineStr">
+      <c r="AK18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9625,7 +9625,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AM18" s="7" t="inlineStr">
+      <c r="AM18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9660,12 +9660,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU18" s="7" t="inlineStr">
+      <c r="AT18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9675,14 +9675,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY18" s="6" t="inlineStr">
@@ -9705,42 +9705,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ18" s="7" t="inlineStr">
+      <c r="BC18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9755,9 +9755,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -9782,9 +9782,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -9797,17 +9797,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9822,7 +9822,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr">
+      <c r="M19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9832,29 +9832,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T19" s="6" t="inlineStr">
@@ -9867,27 +9867,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z19" s="7" t="inlineStr">
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9907,22 +9907,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG19" s="7" t="inlineStr">
+      <c r="AD19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9932,32 +9932,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN19" s="7" t="inlineStr">
+      <c r="AI19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9987,29 +9987,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY19" s="6" t="inlineStr">
@@ -10032,42 +10032,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ19" s="7" t="inlineStr">
+      <c r="BC19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10082,9 +10082,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -10109,9 +10109,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -10124,17 +10124,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10149,7 +10149,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr">
+      <c r="M20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10159,29 +10159,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T20" s="6" t="inlineStr">
@@ -10194,27 +10194,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z20" s="7" t="inlineStr">
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10239,17 +10239,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG20" s="7" t="inlineStr">
+      <c r="AE20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10259,32 +10259,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN20" s="7" t="inlineStr">
+      <c r="AI20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10314,12 +10314,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU20" s="7" t="inlineStr">
+      <c r="AT20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10329,14 +10329,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY20" s="6" t="inlineStr">
@@ -10359,42 +10359,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ20" s="7" t="inlineStr">
+      <c r="BC20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10409,9 +10409,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -10436,9 +10436,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -10451,17 +10451,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10476,7 +10476,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr">
+      <c r="M21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10486,29 +10486,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T21" s="6" t="inlineStr">
@@ -10521,27 +10521,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z21" s="7" t="inlineStr">
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10556,7 +10556,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC21" s="7" t="inlineStr">
+      <c r="AC21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10566,12 +10566,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF21" s="7" t="inlineStr">
+      <c r="AE21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10586,7 +10586,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI21" s="7" t="inlineStr">
+      <c r="AI21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10596,7 +10596,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK21" s="7" t="inlineStr">
+      <c r="AK21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10606,7 +10606,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AM21" s="7" t="inlineStr">
+      <c r="AM21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10641,29 +10641,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY21" s="6" t="inlineStr">
@@ -10686,42 +10686,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ21" s="7" t="inlineStr">
+      <c r="BC21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10736,9 +10736,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -10763,9 +10763,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -10778,17 +10778,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10803,7 +10803,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr">
+      <c r="M22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10813,29 +10813,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
@@ -10848,27 +10848,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z22" s="7" t="inlineStr">
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10893,17 +10893,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG22" s="7" t="inlineStr">
+      <c r="AE22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10913,32 +10913,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN22" s="7" t="inlineStr">
+      <c r="AI22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10968,12 +10968,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU22" s="7" t="inlineStr">
+      <c r="AT22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10983,14 +10983,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY22" s="6" t="inlineStr">
@@ -11013,42 +11013,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ22" s="7" t="inlineStr">
+      <c r="BC22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11063,9 +11063,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -11090,9 +11090,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -11105,17 +11105,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11130,7 +11130,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr">
+      <c r="M23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11140,29 +11140,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T23" s="6" t="inlineStr">
@@ -11175,27 +11175,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z23" s="7" t="inlineStr">
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11215,22 +11215,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG23" s="7" t="inlineStr">
+      <c r="AD23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11240,32 +11240,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN23" s="7" t="inlineStr">
+      <c r="AI23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11295,12 +11295,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU23" s="7" t="inlineStr">
+      <c r="AT23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11310,14 +11310,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY23" s="6" t="inlineStr">
@@ -11340,42 +11340,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ23" s="7" t="inlineStr">
+      <c r="BC23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11390,9 +11390,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -11417,9 +11417,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -11432,17 +11432,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11457,7 +11457,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M24" s="7" t="inlineStr">
+      <c r="M24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11467,29 +11467,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T24" s="6" t="inlineStr">
@@ -11502,27 +11502,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z24" s="7" t="inlineStr">
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11547,17 +11547,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG24" s="7" t="inlineStr">
+      <c r="AE24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11567,32 +11567,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN24" s="7" t="inlineStr">
+      <c r="AI24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11622,12 +11622,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU24" s="7" t="inlineStr">
+      <c r="AT24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11637,14 +11637,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY24" s="6" t="inlineStr">
@@ -11667,42 +11667,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ24" s="7" t="inlineStr">
+      <c r="BC24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11717,9 +11717,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -11744,7 +11744,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -11759,17 +11759,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11784,7 +11784,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M25" s="7" t="inlineStr">
+      <c r="M25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11794,17 +11794,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q25" s="7" t="inlineStr">
+      <c r="O25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11829,27 +11829,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z25" s="7" t="inlineStr">
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11874,17 +11874,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG25" s="7" t="inlineStr">
+      <c r="AE25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11894,32 +11894,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN25" s="7" t="inlineStr">
+      <c r="AI25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11949,12 +11949,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU25" s="7" t="inlineStr">
+      <c r="AT25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11969,7 +11969,7 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX25" s="8" t="inlineStr">
+      <c r="AX25" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -11994,42 +11994,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ25" s="7" t="inlineStr">
+      <c r="BC25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12071,9 +12071,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -12086,17 +12086,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12111,7 +12111,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M26" s="7" t="inlineStr">
+      <c r="M26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12121,29 +12121,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T26" s="6" t="inlineStr">
@@ -12156,27 +12156,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z26" s="7" t="inlineStr">
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12191,7 +12191,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC26" s="7" t="inlineStr">
+      <c r="AC26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12201,17 +12201,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG26" s="7" t="inlineStr">
+      <c r="AE26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12221,32 +12221,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN26" s="7" t="inlineStr">
+      <c r="AI26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12256,7 +12256,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AP26" s="7" t="inlineStr">
+      <c r="AP26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12276,12 +12276,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU26" s="7" t="inlineStr">
+      <c r="AT26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12291,14 +12291,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX26" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY26" s="6" t="inlineStr">
@@ -12321,42 +12321,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ26" s="7" t="inlineStr">
+      <c r="BC26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12371,9 +12371,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -12398,9 +12398,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -12413,17 +12413,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12438,7 +12438,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M27" s="7" t="inlineStr">
+      <c r="M27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12448,29 +12448,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T27" s="6" t="inlineStr">
@@ -12483,27 +12483,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z27" s="7" t="inlineStr">
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12518,7 +12518,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC27" s="7" t="inlineStr">
+      <c r="AC27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12528,12 +12528,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF27" s="7" t="inlineStr">
+      <c r="AE27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12548,7 +12548,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI27" s="7" t="inlineStr">
+      <c r="AI27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12558,7 +12558,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK27" s="7" t="inlineStr">
+      <c r="AK27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12568,7 +12568,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AM27" s="7" t="inlineStr">
+      <c r="AM27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12583,7 +12583,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AP27" s="7" t="inlineStr">
+      <c r="AP27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12603,29 +12603,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX27" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY27" s="6" t="inlineStr">
@@ -12648,42 +12648,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ27" s="7" t="inlineStr">
+      <c r="BC27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12698,9 +12698,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -12725,9 +12725,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -12740,17 +12740,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12765,7 +12765,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M28" s="7" t="inlineStr">
+      <c r="M28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12775,29 +12775,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T28" s="6" t="inlineStr">
@@ -12810,27 +12810,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z28" s="7" t="inlineStr">
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12845,7 +12845,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC28" s="7" t="inlineStr">
+      <c r="AC28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12855,17 +12855,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG28" s="7" t="inlineStr">
+      <c r="AE28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12875,32 +12875,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN28" s="7" t="inlineStr">
+      <c r="AI28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12910,7 +12910,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AP28" s="7" t="inlineStr">
+      <c r="AP28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12930,12 +12930,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU28" s="7" t="inlineStr">
+      <c r="AT28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12945,14 +12945,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY28" s="6" t="inlineStr">
@@ -12975,42 +12975,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ28" s="7" t="inlineStr">
+      <c r="BC28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13025,9 +13025,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -13067,17 +13067,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J29" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13092,7 +13092,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M29" s="7" t="inlineStr">
+      <c r="M29" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13102,17 +13102,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q29" s="7" t="inlineStr">
+      <c r="O29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q29" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13137,27 +13137,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z29" s="7" t="inlineStr">
+      <c r="V29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z29" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13182,17 +13182,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG29" s="7" t="inlineStr">
+      <c r="AE29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG29" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13202,32 +13202,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN29" s="7" t="inlineStr">
+      <c r="AI29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN29" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13257,17 +13257,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV29" s="7" t="inlineStr">
+      <c r="AT29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV29" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13277,7 +13277,7 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX29" s="8" t="inlineStr">
+      <c r="AX29" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -13302,42 +13302,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ29" s="7" t="inlineStr">
+      <c r="BC29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ29" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13373,7 +13373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13407,7 +13407,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STM32L4Q5AG</t>
+          <t>STM32L4P5RE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -13429,7 +13429,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32L4Q5AG</t>
+          <t>STM32L4P5RE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -13451,7 +13451,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32L4Q5AG</t>
+          <t>STM32L4P5RE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -13473,7 +13473,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32L4P5AE</t>
+          <t>STM32L4P5ZG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -13495,7 +13495,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32L4P5AE</t>
+          <t>STM32L4P5ZG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -13517,20 +13517,1076 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>STM32L4P5ZG</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>STM32L4Q5CG</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>STM32L4Q5CG</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STM32L4Q5CG</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>STM32L4P5ZE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STM32L4P5ZE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STM32L4P5ZE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>STM32L4P5QG</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>STM32L4P5QG</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>STM32L4P5QG</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>STM32L4Q5RG</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>STM32L4Q5RG</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>STM32L4Q5RG</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>STM32L4P5VG</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>STM32L4P5VG</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>STM32L4P5VG</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>STM32L4P5QE</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>STM32L4P5QE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>STM32L4P5QE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>STM32L4Q5ZG</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>STM32L4Q5ZG</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>STM32L4Q5ZG</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>STM32L4P5VE</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>STM32L4P5VE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>STM32L4P5VE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>STM32L4Q5VG</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>STM32L4Q5VG</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>STM32L4Q5VG</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>STM32L4Q5QG</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>STM32L4Q5QG</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>STM32L4Q5QG</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>STM32L4P5AG</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>STM32L4P5AG</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>STM32L4P5AG</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>STM32L4Q5AG</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>STM32L4Q5AG</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>STM32L4Q5AG</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>STM32L4P5CG</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>STM32L4P5CG</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>STM32L4P5CG</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>STM32L4P5CE</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>STM32L4P5CE</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>STM32L4P5CE</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>STM32L4P5RG</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>STM32L4P5RG</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>STM32L4P5RG</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>STM32L4P5AE</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>STM32L4P5AE</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>STM32L4P5AE</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
         <is>
           <t>Supply Voltage (V) min</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Table 21. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>

--- a/product_selector_out/STM32L4P5-Q5.xlsx
+++ b/product_selector_out/STM32L4P5-Q5.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM29"/>
+  <dimension ref="A1:BN29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828125" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4q5ag.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4q5ag.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
@@ -3603,6 +3645,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4q5ag.pdf</t>
         </is>
       </c>
@@ -4257,6 +4309,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
@@ -4584,6 +4641,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4q5ag.pdf</t>
         </is>
       </c>
@@ -4911,6 +4973,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4q5ag.pdf</t>
         </is>
       </c>
@@ -5238,6 +5305,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
@@ -5565,6 +5637,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4q5ag.pdf</t>
         </is>
       </c>
@@ -5892,6 +5969,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
@@ -6219,6 +6301,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
@@ -6546,6 +6633,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
@@ -6873,12 +6965,17 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -6899,16 +6996,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -6921,6 +7016,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -6940,7 +7036,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -6975,7 +7073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM29"/>
+  <dimension ref="A1:BN29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7043,6 +7141,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7376,6 +7475,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -7471,6 +7575,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -7793,7 +7898,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8120,7 +8230,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8447,7 +8562,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8774,7 +8894,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9101,7 +9226,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9428,7 +9558,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9755,7 +9890,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10082,7 +10222,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10409,7 +10554,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10736,7 +10886,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11063,7 +11218,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11390,7 +11550,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11717,7 +11882,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12044,7 +12214,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12371,7 +12546,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12698,7 +12878,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13025,7 +13210,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13352,7 +13542,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13360,8 +13555,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
